--- a/DSA/Google_DSA_Interview_Prep.xlsx
+++ b/DSA/Google_DSA_Interview_Prep.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MaitySom\Desktop\Somneel\Somneel_Maity\K_Tech\DSA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E9E44CB-C0F3-4D52-92B5-5B85CDD14D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FD68C9B-D7B9-4154-8CF7-2207830BE070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="11" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -6803,7 +6803,7 @@
         <v>88</v>
       </c>
       <c r="G12" s="64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -6849,7 +6849,7 @@
         <v>95</v>
       </c>
       <c r="G14" s="64" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7" ht="18" customHeight="1" x14ac:dyDescent="0.3">
